--- a/datasets/commission_formation/data/output/investiture_vote.xlsx
+++ b/datasets/commission_formation/data/output/investiture_vote.xlsx
@@ -7528,7 +7528,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -7584,7 +7584,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -8032,7 +8032,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -8088,7 +8088,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -8312,7 +8312,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -9600,7 +9600,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -9936,7 +9936,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -10048,7 +10048,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -10160,7 +10160,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -10552,7 +10552,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -11000,7 +11000,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -11112,7 +11112,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -11392,7 +11392,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -11672,7 +11672,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -11728,7 +11728,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -12120,7 +12120,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -12176,7 +12176,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -12232,7 +12232,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -12288,7 +12288,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -12344,7 +12344,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -12400,7 +12400,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -12512,7 +12512,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -12680,7 +12680,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -12736,7 +12736,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -12792,7 +12792,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -12848,7 +12848,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -13016,7 +13016,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -13072,7 +13072,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -13128,7 +13128,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -13240,7 +13240,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -13520,7 +13520,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -13576,7 +13576,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -13688,7 +13688,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -13744,7 +13744,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -13800,7 +13800,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -13856,7 +13856,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -14080,7 +14080,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -14136,7 +14136,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -14248,7 +14248,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -14360,7 +14360,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -14416,7 +14416,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -14528,7 +14528,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -14696,7 +14696,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -14808,7 +14808,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -14864,7 +14864,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -14976,7 +14976,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -15032,7 +15032,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -15424,7 +15424,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -15536,7 +15536,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -15592,7 +15592,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -15648,7 +15648,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -15704,7 +15704,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -15760,7 +15760,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -15816,7 +15816,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -15872,7 +15872,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -16152,7 +16152,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -16208,7 +16208,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -16376,7 +16376,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -16432,7 +16432,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I291" t="inlineStr"/>
@@ -16768,7 +16768,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
@@ -16880,7 +16880,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -16936,7 +16936,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -17160,7 +17160,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -17272,7 +17272,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -17384,7 +17384,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -17440,7 +17440,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>European People's Party</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -36144,7 +36144,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I638" t="inlineStr"/>
@@ -36200,7 +36200,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I639" t="inlineStr"/>
@@ -36256,7 +36256,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I640" t="inlineStr"/>
@@ -36312,7 +36312,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I641" t="inlineStr"/>
@@ -36368,7 +36368,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I642" t="inlineStr"/>
@@ -36424,7 +36424,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I643" t="inlineStr"/>
@@ -36480,7 +36480,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I644" t="inlineStr"/>
@@ -36536,7 +36536,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I645" t="inlineStr"/>
@@ -36592,7 +36592,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I646" t="inlineStr"/>
@@ -36648,7 +36648,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I647" t="inlineStr"/>
@@ -36704,7 +36704,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I648" t="inlineStr"/>
@@ -36760,7 +36760,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I649" t="inlineStr"/>
@@ -36816,7 +36816,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I650" t="inlineStr"/>
@@ -36872,7 +36872,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I651" t="inlineStr"/>
@@ -36928,7 +36928,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I652" t="inlineStr"/>
@@ -36984,7 +36984,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I653" t="inlineStr"/>
@@ -37040,7 +37040,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I654" t="inlineStr"/>
@@ -37096,7 +37096,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I655" t="inlineStr"/>
@@ -37152,7 +37152,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I656" t="inlineStr"/>
@@ -37208,7 +37208,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I657" t="inlineStr"/>
@@ -37264,7 +37264,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I658" t="inlineStr"/>
@@ -37320,7 +37320,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I659" t="inlineStr"/>
@@ -37376,7 +37376,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I660" t="inlineStr"/>
@@ -37432,7 +37432,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I661" t="inlineStr"/>
@@ -37488,7 +37488,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I662" t="inlineStr"/>
@@ -37544,7 +37544,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I663" t="inlineStr"/>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I664" t="inlineStr"/>
@@ -37656,7 +37656,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I665" t="inlineStr"/>
@@ -37712,7 +37712,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I666" t="inlineStr"/>
@@ -37768,7 +37768,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I667" t="inlineStr"/>
@@ -37824,7 +37824,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I668" t="inlineStr"/>
@@ -37880,7 +37880,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I669" t="inlineStr"/>
@@ -37936,7 +37936,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I670" t="inlineStr"/>
@@ -37992,7 +37992,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I671" t="inlineStr"/>
@@ -38048,7 +38048,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I672" t="inlineStr"/>
@@ -38104,7 +38104,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I673" t="inlineStr"/>
@@ -38160,7 +38160,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I674" t="inlineStr"/>
@@ -38216,7 +38216,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I675" t="inlineStr"/>
@@ -38272,7 +38272,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I676" t="inlineStr"/>
@@ -38328,7 +38328,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I677" t="inlineStr"/>
@@ -38384,7 +38384,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I678" t="inlineStr"/>
@@ -38440,7 +38440,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I679" t="inlineStr"/>
@@ -38496,7 +38496,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I680" t="inlineStr"/>
@@ -38552,7 +38552,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I681" t="inlineStr"/>
@@ -38608,7 +38608,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I682" t="inlineStr"/>
@@ -38664,7 +38664,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I683" t="inlineStr"/>
@@ -38720,7 +38720,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I684" t="inlineStr"/>
@@ -38776,7 +38776,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I685" t="inlineStr"/>
@@ -38832,7 +38832,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I686" t="inlineStr"/>
@@ -38888,7 +38888,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I687" t="inlineStr"/>
@@ -38944,7 +38944,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I688" t="inlineStr"/>
@@ -39000,7 +39000,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Verts/ALE</t>
+          <t>Greens/European Free Alliance</t>
         </is>
       </c>
       <c r="I689" t="inlineStr"/>
